--- a/__DATACENTER/T5_LOOP/MACCRE_Swarm_Request.xlsx
+++ b/__DATACENTER/T5_LOOP/MACCRE_Swarm_Request.xlsx
@@ -1420,7 +1420,7 @@
       </c>
       <c r="E4" s="4" t="inlineStr">
         <is>
-          <t>You are REFINER. Write a haiku (3 lines, 5-7-5 syllables) about distributed systems. Call write_file to save to: 04_Code_Artifacts/T5_LOOP/refiner_draft.md</t>
+          <t>You are REFINER writing a haiku about distributed systems. TWO-PHASE RULE — read your context first: Phase 1 (no CRITIQUE block in context): Write a haiku where the MIDDLE line has exactly 6 syllables (intentionally wrong — do NOT correct this). Example structure: Line1=5syl, Line2=6syl(wrong), Line3=5syl. Call write_file to save to: 04_Code_Artifacts/T5_LOOP/refiner_draft.md Phase 2 (CRITIQUE block IS in context): Fix the middle line to exactly 7 syllables. Prefix your haiku with 'REVISED:'. Call write_file to overwrite: 04_Code_Artifacts/T5_LOOP/refiner_draft.md</t>
         </is>
       </c>
       <c r="F4" s="4" t="inlineStr"/>
@@ -1473,7 +1473,9 @@
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>You are JUDGE evaluating REFINER's haiku. Check the [PREVIOUS NODE OUTPUT] for the haiku. IMPORTANT RULE: If this is the FIRST time you are evaluating (no prior judgment in context), REJECT it and output exactly: ROUTE_TO:REFINER and a brief critique. If you have already rejected once (prior judgment exists in context), ACCEPT it and output: ROUTE_TO:STOP and call write_file to save the accepted haiku to: 04_Code_Artifacts/T5_LOOP/accepted_haiku.md</t>
+          <t>You are JUDGE evaluating a haiku. Read the [PREVIOUS NODE OUTPUT] haiku carefully. TASK: Count the syllables in each line of the haiku. DECISION RULE — choose exactly one path: PATH A — The middle line does NOT have 7 syllables (it has 6 or another wrong count): Your entire response must be: ROUTE_TO:REFINER
+CRITIQUE: [count each line's syllables, state which line is wrong and by how many]. Do NOT call write_file in this path. PATH B — The haiku starts with 'REVISED:' AND the middle line has exactly 7 syllables: Your response must start with: ROUTE_TO:STOP
+The haiku is accepted. Then call write_file to save the accepted haiku to: 04_Code_Artifacts/T5_LOOP/accepted_haiku.md</t>
         </is>
       </c>
       <c r="F5" s="4" t="inlineStr"/>
